--- a/Safe_Results/SA_Capacity_Costs/SA_Capacity_Costs_LPLB.xlsx
+++ b/Safe_Results/SA_Capacity_Costs/SA_Capacity_Costs_LPLB.xlsx
@@ -626,10 +626,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2803.508</v>
+        <v>1769.773</v>
       </c>
       <c r="G4" t="n">
-        <v>2608.893</v>
+        <v>1575.158</v>
       </c>
       <c r="H4" t="n">
         <v>194.615</v>
@@ -864,10 +864,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2996.173</v>
+        <v>1799.52</v>
       </c>
       <c r="G4" t="n">
-        <v>2883.935</v>
+        <v>1687.282</v>
       </c>
       <c r="H4" t="n">
         <v>112.238</v>
@@ -1102,10 +1102,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2996.173</v>
+        <v>1799.52</v>
       </c>
       <c r="G4" t="n">
-        <v>2883.935</v>
+        <v>1687.282</v>
       </c>
       <c r="H4" t="n">
         <v>112.238</v>
@@ -1340,10 +1340,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2996.173</v>
+        <v>1799.52</v>
       </c>
       <c r="G4" t="n">
-        <v>2883.935</v>
+        <v>1687.282</v>
       </c>
       <c r="H4" t="n">
         <v>112.238</v>
@@ -1578,10 +1578,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2996.173</v>
+        <v>1799.52</v>
       </c>
       <c r="G4" t="n">
-        <v>2883.935</v>
+        <v>1687.282</v>
       </c>
       <c r="H4" t="n">
         <v>112.238</v>
